--- a/requeteMapping/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/requeteMapping/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T13:04:19+00:00</t>
+    <t>2026-06-08T14:21:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/requeteMapping/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/requeteMapping/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T14:21:16+00:00</t>
+    <t>2026-06-08T15:10:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/requeteMapping/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/requeteMapping/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T15:10:46+00:00</t>
+    <t>2026-06-09T09:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
